--- a/client/public/products/pack1-pm-essentials/igce-calculator.xlsx
+++ b/client/public/products/pack1-pm-essentials/igce-calculator.xlsx
@@ -11,19 +11,23 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ODC &amp; Travel" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IGCE Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'ODC &amp; Travel'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'IGCE Summary'!$A$1:$F$45</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="\$#,##0"/>
+    <numFmt numFmtId="167" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="30">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -151,8 +155,63 @@
       <color rgb="FF01696F"/>
       <sz val="13"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF0D1B2A"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0001696F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF6B7280"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF0D1B2A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF6B7280"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF0D1B2A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="00333333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF6B7280"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -171,8 +230,23 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0D1B2A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F4F6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -206,6 +280,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE5E7EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE5E7EB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE5E7EB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE5E7EB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -217,7 +305,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -396,6 +484,53 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="22" fillId="6" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="19" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -466,6 +601,127 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>IGCE Cost by Category (3-Year Total)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'IGCE Summary'!F5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'IGCE Summary'!$B$6:$B$10</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'IGCE Summary'!$F$6:$F$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Cost ($)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -649,7 +905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="B2:N21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="30" min="1" max="1"/>
@@ -663,7 +919,6 @@
     <col width="18" customWidth="1" style="30" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="30" customHeight="1" s="31">
       <c r="B2" s="32" t="inlineStr">
         <is>
@@ -678,7 +933,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1" s="31">
       <c r="B5" s="34" t="inlineStr">
         <is>
@@ -757,25 +1011,25 @@
           <t>Overall program leadership, status reporting, EVM oversight</t>
         </is>
       </c>
-      <c r="D6" s="37" t="n">
+      <c r="D6" s="60" t="n">
         <v>1920</v>
       </c>
-      <c r="E6" s="37" t="n">
+      <c r="E6" s="60" t="n">
         <v>1920</v>
       </c>
-      <c r="F6" s="37" t="n">
+      <c r="F6" s="60" t="n">
         <v>1920</v>
       </c>
-      <c r="G6" s="38" t="n">
+      <c r="G6" s="61" t="n">
         <v>165</v>
       </c>
-      <c r="H6" s="39" t="n">
+      <c r="H6" s="62" t="n">
         <v>0.32</v>
       </c>
-      <c r="I6" s="39" t="n">
+      <c r="I6" s="62" t="n">
         <v>0.45</v>
       </c>
-      <c r="J6" s="39" t="n">
+      <c r="J6" s="62" t="n">
         <v>0.08</v>
       </c>
       <c r="K6" s="40">
@@ -806,25 +1060,25 @@
           <t>Systems architecture, requirements analysis, design reviews</t>
         </is>
       </c>
-      <c r="D7" s="37" t="n">
+      <c r="D7" s="60" t="n">
         <v>1880</v>
       </c>
-      <c r="E7" s="37" t="n">
+      <c r="E7" s="60" t="n">
         <v>1880</v>
       </c>
-      <c r="F7" s="37" t="n">
+      <c r="F7" s="60" t="n">
         <v>1880</v>
       </c>
-      <c r="G7" s="38" t="n">
+      <c r="G7" s="61" t="n">
         <v>145</v>
       </c>
-      <c r="H7" s="39" t="n">
+      <c r="H7" s="62" t="n">
         <v>0.32</v>
       </c>
-      <c r="I7" s="39" t="n">
+      <c r="I7" s="62" t="n">
         <v>0.45</v>
       </c>
-      <c r="J7" s="39" t="n">
+      <c r="J7" s="62" t="n">
         <v>0.08</v>
       </c>
       <c r="K7" s="40">
@@ -855,25 +1109,25 @@
           <t>Requirements traceability, test support, documentation</t>
         </is>
       </c>
-      <c r="D8" s="37" t="n">
+      <c r="D8" s="60" t="n">
         <v>1920</v>
       </c>
-      <c r="E8" s="37" t="n">
+      <c r="E8" s="60" t="n">
         <v>1920</v>
       </c>
-      <c r="F8" s="37" t="n">
+      <c r="F8" s="60" t="n">
         <v>1920</v>
       </c>
-      <c r="G8" s="38" t="n">
+      <c r="G8" s="61" t="n">
         <v>95</v>
       </c>
-      <c r="H8" s="39" t="n">
+      <c r="H8" s="62" t="n">
         <v>0.32</v>
       </c>
-      <c r="I8" s="39" t="n">
+      <c r="I8" s="62" t="n">
         <v>0.45</v>
       </c>
-      <c r="J8" s="39" t="n">
+      <c r="J8" s="62" t="n">
         <v>0.08</v>
       </c>
       <c r="K8" s="40">
@@ -904,25 +1158,25 @@
           <t>Contract administration, modifications, compliance monitoring</t>
         </is>
       </c>
-      <c r="D9" s="37" t="n">
+      <c r="D9" s="60" t="n">
         <v>960</v>
       </c>
-      <c r="E9" s="37" t="n">
+      <c r="E9" s="60" t="n">
         <v>960</v>
       </c>
-      <c r="F9" s="37" t="n">
+      <c r="F9" s="60" t="n">
         <v>960</v>
       </c>
-      <c r="G9" s="38" t="n">
+      <c r="G9" s="61" t="n">
         <v>110</v>
       </c>
-      <c r="H9" s="39" t="n">
+      <c r="H9" s="62" t="n">
         <v>0.32</v>
       </c>
-      <c r="I9" s="39" t="n">
+      <c r="I9" s="62" t="n">
         <v>0.45</v>
       </c>
-      <c r="J9" s="39" t="n">
+      <c r="J9" s="62" t="n">
         <v>0.08</v>
       </c>
       <c r="K9" s="40">
@@ -953,25 +1207,25 @@
           <t>EVM analysis, cost reporting, budget tracking, variance analysis</t>
         </is>
       </c>
-      <c r="D10" s="37" t="n">
+      <c r="D10" s="60" t="n">
         <v>1920</v>
       </c>
-      <c r="E10" s="37" t="n">
+      <c r="E10" s="60" t="n">
         <v>1920</v>
       </c>
-      <c r="F10" s="37" t="n">
+      <c r="F10" s="60" t="n">
         <v>1920</v>
       </c>
-      <c r="G10" s="38" t="n">
+      <c r="G10" s="61" t="n">
         <v>105</v>
       </c>
-      <c r="H10" s="39" t="n">
+      <c r="H10" s="62" t="n">
         <v>0.32</v>
       </c>
-      <c r="I10" s="39" t="n">
+      <c r="I10" s="62" t="n">
         <v>0.45</v>
       </c>
-      <c r="J10" s="39" t="n">
+      <c r="J10" s="62" t="n">
         <v>0.08</v>
       </c>
       <c r="K10" s="40">
@@ -1002,25 +1256,25 @@
           <t>CDRL preparation, documentation, SOPs, user manuals</t>
         </is>
       </c>
-      <c r="D11" s="37" t="n">
+      <c r="D11" s="60" t="n">
         <v>1440</v>
       </c>
-      <c r="E11" s="37" t="n">
+      <c r="E11" s="60" t="n">
         <v>1440</v>
       </c>
-      <c r="F11" s="37" t="n">
+      <c r="F11" s="60" t="n">
         <v>1440</v>
       </c>
-      <c r="G11" s="38" t="n">
+      <c r="G11" s="61" t="n">
         <v>75</v>
       </c>
-      <c r="H11" s="39" t="n">
+      <c r="H11" s="62" t="n">
         <v>0.32</v>
       </c>
-      <c r="I11" s="39" t="n">
+      <c r="I11" s="62" t="n">
         <v>0.45</v>
       </c>
-      <c r="J11" s="39" t="n">
+      <c r="J11" s="62" t="n">
         <v>0.08</v>
       </c>
       <c r="K11" s="40">
@@ -1051,25 +1305,25 @@
           <t>Quality management, audits, CMMI compliance, process improvement</t>
         </is>
       </c>
-      <c r="D12" s="37" t="n">
+      <c r="D12" s="60" t="n">
         <v>960</v>
       </c>
-      <c r="E12" s="37" t="n">
+      <c r="E12" s="60" t="n">
         <v>960</v>
       </c>
-      <c r="F12" s="37" t="n">
+      <c r="F12" s="60" t="n">
         <v>960</v>
       </c>
-      <c r="G12" s="38" t="n">
+      <c r="G12" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="H12" s="39" t="n">
+      <c r="H12" s="62" t="n">
         <v>0.32</v>
       </c>
-      <c r="I12" s="39" t="n">
+      <c r="I12" s="62" t="n">
         <v>0.45</v>
       </c>
-      <c r="J12" s="39" t="n">
+      <c r="J12" s="62" t="n">
         <v>0.08</v>
       </c>
       <c r="K12" s="40">
@@ -1100,25 +1354,25 @@
           <t>Program office administration, travel coordination, records management</t>
         </is>
       </c>
-      <c r="D13" s="37" t="n">
+      <c r="D13" s="60" t="n">
         <v>1920</v>
       </c>
-      <c r="E13" s="37" t="n">
+      <c r="E13" s="60" t="n">
         <v>1920</v>
       </c>
-      <c r="F13" s="37" t="n">
+      <c r="F13" s="60" t="n">
         <v>1920</v>
       </c>
-      <c r="G13" s="38" t="n">
+      <c r="G13" s="61" t="n">
         <v>55</v>
       </c>
-      <c r="H13" s="39" t="n">
+      <c r="H13" s="62" t="n">
         <v>0.32</v>
       </c>
-      <c r="I13" s="39" t="n">
+      <c r="I13" s="62" t="n">
         <v>0.45</v>
       </c>
-      <c r="J13" s="39" t="n">
+      <c r="J13" s="62" t="n">
         <v>0.08</v>
       </c>
       <c r="K13" s="40">
@@ -1149,25 +1403,25 @@
           <t>Subcontractor oversight, performance monitoring, consent coordination</t>
         </is>
       </c>
-      <c r="D14" s="37" t="n">
+      <c r="D14" s="60" t="n">
         <v>960</v>
       </c>
-      <c r="E14" s="37" t="n">
+      <c r="E14" s="60" t="n">
         <v>960</v>
       </c>
-      <c r="F14" s="37" t="n">
+      <c r="F14" s="60" t="n">
         <v>960</v>
       </c>
-      <c r="G14" s="38" t="n">
+      <c r="G14" s="61" t="n">
         <v>120</v>
       </c>
-      <c r="H14" s="39" t="n">
+      <c r="H14" s="62" t="n">
         <v>0.32</v>
       </c>
-      <c r="I14" s="39" t="n">
+      <c r="I14" s="62" t="n">
         <v>0.45</v>
       </c>
-      <c r="J14" s="39" t="n">
+      <c r="J14" s="62" t="n">
         <v>0.08</v>
       </c>
       <c r="K14" s="40">
@@ -1198,25 +1452,25 @@
           <t>Network administration, cybersecurity compliance, system maintenance</t>
         </is>
       </c>
-      <c r="D15" s="37" t="n">
+      <c r="D15" s="60" t="n">
         <v>1920</v>
       </c>
-      <c r="E15" s="37" t="n">
+      <c r="E15" s="60" t="n">
         <v>1920</v>
       </c>
-      <c r="F15" s="37" t="n">
+      <c r="F15" s="60" t="n">
         <v>1920</v>
       </c>
-      <c r="G15" s="38" t="n">
+      <c r="G15" s="61" t="n">
         <v>115</v>
       </c>
-      <c r="H15" s="39" t="n">
+      <c r="H15" s="62" t="n">
         <v>0.32</v>
       </c>
-      <c r="I15" s="39" t="n">
+      <c r="I15" s="62" t="n">
         <v>0.45</v>
       </c>
-      <c r="J15" s="39" t="n">
+      <c r="J15" s="62" t="n">
         <v>0.08</v>
       </c>
       <c r="K15" s="40">
@@ -1236,7 +1490,6 @@
         <v/>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="24.75" customHeight="1" s="31">
       <c r="B17" s="42" t="inlineStr">
         <is>
@@ -1277,7 +1530,6 @@
         <v/>
       </c>
     </row>
-    <row r="18"/>
     <row r="19" ht="34.5" customHeight="1" s="31">
       <c r="B19" s="46" t="inlineStr">
         <is>
@@ -1285,7 +1537,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21" ht="15" customHeight="1" s="31">
       <c r="B21" s="47" t="inlineStr">
         <is>
@@ -1294,6 +1545,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="4">
     <mergeCell ref="B3:N3"/>
     <mergeCell ref="B2:N2"/>
@@ -1308,637 +1560,811 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="B2:G32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" style="30" min="1" max="1"/>
-    <col width="30" customWidth="1" style="30" min="2" max="2"/>
-    <col width="14" customWidth="1" style="30" min="3" max="5"/>
-    <col width="16" customWidth="1" style="30" min="6" max="6"/>
-    <col width="40" customWidth="1" style="30" min="7" max="7"/>
+    <col width="2.5" customWidth="1" style="31" min="1" max="1"/>
+    <col width="32" customWidth="1" style="31" min="2" max="2"/>
+    <col width="13" customWidth="1" style="31" min="3" max="3"/>
+    <col width="13" customWidth="1" style="31" min="4" max="4"/>
+    <col width="13" customWidth="1" style="31" min="5" max="5"/>
+    <col width="13" customWidth="1" style="31" min="6" max="6"/>
+    <col width="46" customWidth="1" style="31" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="30" customHeight="1" s="31">
-      <c r="B2" s="32" t="inlineStr">
+    <row r="2">
+      <c r="B2" s="65" t="inlineStr">
         <is>
           <t>Other Direct Costs (ODC) &amp; Travel Estimate</t>
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4" ht="15" customHeight="1" s="31">
-      <c r="B4" s="48" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="66" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="C4" s="48" t="inlineStr">
+      <c r="C4" s="66" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
-      <c r="D4" s="48" t="inlineStr">
+      <c r="D4" s="66" t="inlineStr">
         <is>
           <t>Year 2</t>
         </is>
       </c>
-      <c r="E4" s="48" t="inlineStr">
+      <c r="E4" s="66" t="inlineStr">
         <is>
           <t>Year 3</t>
         </is>
       </c>
-      <c r="F4" s="48" t="inlineStr">
+      <c r="F4" s="66" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="G4" s="48" t="inlineStr">
+      <c r="G4" s="66" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="21.75" customHeight="1" s="31">
-      <c r="B5" s="49" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="67" t="inlineStr">
         <is>
           <t>MATERIALS</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" s="31">
-      <c r="B6" s="50" t="inlineStr">
+      <c r="C5" s="68" t="n"/>
+      <c r="D5" s="68" t="n"/>
+      <c r="E5" s="68" t="n"/>
+      <c r="F5" s="68" t="n"/>
+      <c r="G5" s="68" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="69" t="inlineStr">
         <is>
           <t>Software Licenses (COTS)</t>
         </is>
       </c>
-      <c r="C6" s="40" t="n">
+      <c r="C6" s="70" t="n">
         <v>85000</v>
       </c>
-      <c r="D6" s="40" t="n">
+      <c r="D6" s="70" t="n">
         <v>87550</v>
       </c>
-      <c r="E6" s="40" t="n">
+      <c r="E6" s="70" t="n">
         <v>90177</v>
       </c>
-      <c r="F6" s="41">
+      <c r="F6" s="71">
         <f>C6+D6+E6</f>
         <v/>
       </c>
-      <c r="G6" s="51" t="inlineStr">
+      <c r="G6" s="72" t="inlineStr">
         <is>
           <t>Annual licenses for JIRA, Confluence, MS Project; 3% annual escalation</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" s="31">
-      <c r="B7" s="50" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="69" t="inlineStr">
         <is>
           <t>Hardware/Equipment</t>
         </is>
       </c>
-      <c r="C7" s="40" t="n">
+      <c r="C7" s="70" t="n">
         <v>45000</v>
       </c>
-      <c r="D7" s="40" t="n">
+      <c r="D7" s="70" t="n">
         <v>15000</v>
       </c>
-      <c r="E7" s="40" t="n">
+      <c r="E7" s="70" t="n">
         <v>15000</v>
       </c>
-      <c r="F7" s="41">
+      <c r="F7" s="71">
         <f>C7+D7+E7</f>
         <v/>
       </c>
-      <c r="G7" s="51" t="inlineStr">
+      <c r="G7" s="72" t="inlineStr">
         <is>
           <t>Initial workstation setup Y1; replacement/refresh Y2-Y3</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1" s="31">
-      <c r="B8" s="50" t="inlineStr">
+    <row r="8">
+      <c r="B8" s="69" t="inlineStr">
         <is>
           <t>Office Supplies &amp; Consumables</t>
         </is>
       </c>
-      <c r="C8" s="40" t="n">
+      <c r="C8" s="70" t="n">
         <v>8000</v>
       </c>
-      <c r="D8" s="40" t="n">
+      <c r="D8" s="70" t="n">
         <v>8000</v>
       </c>
-      <c r="E8" s="40" t="n">
+      <c r="E8" s="70" t="n">
         <v>8000</v>
       </c>
-      <c r="F8" s="41">
+      <c r="F8" s="71">
         <f>C8+D8+E8</f>
         <v/>
       </c>
-      <c r="G8" s="51" t="inlineStr">
+      <c r="G8" s="72" t="inlineStr">
         <is>
           <t>Program office supplies, printing, reproduction</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10" ht="21.75" customHeight="1" s="31">
-      <c r="B10" s="49" t="inlineStr">
+    <row r="9">
+      <c r="B9" s="73" t="inlineStr">
+        <is>
+          <t>Materials Subtotal</t>
+        </is>
+      </c>
+      <c r="C9" s="74">
+        <f>SUM(C6:C8)</f>
+        <v/>
+      </c>
+      <c r="D9" s="74">
+        <f>SUM(D6:D8)</f>
+        <v/>
+      </c>
+      <c r="E9" s="74">
+        <f>SUM(E6:E8)</f>
+        <v/>
+      </c>
+      <c r="F9" s="74">
+        <f>SUM(F6:F8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="67" t="inlineStr">
         <is>
           <t>TRAVEL</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="30" customHeight="1" s="31">
-      <c r="B11" s="50" t="inlineStr">
+      <c r="C11" s="68" t="n"/>
+      <c r="D11" s="68" t="n"/>
+      <c r="E11" s="68" t="n"/>
+      <c r="F11" s="68" t="n"/>
+      <c r="G11" s="68" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="69" t="inlineStr">
         <is>
           <t>CONUS Travel — Program Reviews</t>
         </is>
       </c>
-      <c r="C11" s="40" t="n">
+      <c r="C12" s="70" t="n">
         <v>36000</v>
       </c>
-      <c r="D11" s="40" t="n">
+      <c r="D12" s="70" t="n">
         <v>36000</v>
       </c>
-      <c r="E11" s="40" t="n">
+      <c r="E12" s="70" t="n">
         <v>36000</v>
       </c>
-      <c r="F11" s="41">
-        <f>C11+D11+E11</f>
-        <v/>
-      </c>
-      <c r="G11" s="51" t="inlineStr">
-        <is>
-          <t>6 trips/yr × 2 travelers × $3,000/trip (per JTR rates)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1" s="31">
-      <c r="B12" s="50" t="inlineStr">
+      <c r="F12" s="71">
+        <f>C12+D12+E12</f>
+        <v/>
+      </c>
+      <c r="G12" s="72" t="inlineStr">
+        <is>
+          <t>6 trips/yr x 2 travelers x $3,000/trip (per JTR rates)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="69" t="inlineStr">
         <is>
           <t>CONUS Travel — Test Events</t>
         </is>
       </c>
-      <c r="C12" s="40" t="n">
+      <c r="C13" s="70" t="n">
         <v>24000</v>
       </c>
-      <c r="D12" s="40" t="n">
+      <c r="D13" s="70" t="n">
         <v>24000</v>
       </c>
-      <c r="E12" s="40" t="n">
+      <c r="E13" s="70" t="n">
         <v>24000</v>
       </c>
-      <c r="F12" s="41">
-        <f>C12+D12+E12</f>
-        <v/>
-      </c>
-      <c r="G12" s="51" t="inlineStr">
-        <is>
-          <t>4 test events/yr × 2 travelers × $3,000/trip</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1" s="31">
-      <c r="B13" s="50" t="inlineStr">
+      <c r="F13" s="71">
+        <f>C13+D13+E13</f>
+        <v/>
+      </c>
+      <c r="G13" s="72" t="inlineStr">
+        <is>
+          <t>4 test events/yr x 2 travelers x $3,000/trip</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="69" t="inlineStr">
         <is>
           <t>OCONUS Travel</t>
         </is>
       </c>
-      <c r="C13" s="40" t="n">
+      <c r="C14" s="70" t="n">
         <v>15000</v>
       </c>
-      <c r="D13" s="40" t="n">
+      <c r="D14" s="70" t="n">
         <v>15000</v>
       </c>
-      <c r="E13" s="40" t="n">
+      <c r="E14" s="70" t="n">
         <v>15000</v>
       </c>
-      <c r="F13" s="41">
-        <f>C13+D13+E13</f>
-        <v/>
-      </c>
-      <c r="G13" s="51" t="inlineStr">
-        <is>
-          <t>1 trip/yr × 2 travelers to theater for site assessment</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1" s="31">
-      <c r="B14" s="50" t="inlineStr">
+      <c r="F14" s="71">
+        <f>C14+D14+E14</f>
+        <v/>
+      </c>
+      <c r="G14" s="72" t="inlineStr">
+        <is>
+          <t>1 trip/yr x 2 travelers to theater for site assessment</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="69" t="inlineStr">
         <is>
           <t>Local Travel</t>
         </is>
       </c>
-      <c r="C14" s="40" t="n">
+      <c r="C15" s="70" t="n">
         <v>6000</v>
       </c>
-      <c r="D14" s="40" t="n">
+      <c r="D15" s="70" t="n">
         <v>6000</v>
       </c>
-      <c r="E14" s="40" t="n">
+      <c r="E15" s="70" t="n">
         <v>6000</v>
       </c>
-      <c r="F14" s="41">
-        <f>C14+D14+E14</f>
-        <v/>
-      </c>
-      <c r="G14" s="51" t="inlineStr">
+      <c r="F15" s="71">
+        <f>C15+D15+E15</f>
+        <v/>
+      </c>
+      <c r="G15" s="72" t="inlineStr">
         <is>
           <t>Monthly travel to government site; mileage per GSA rate</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16" ht="21.75" customHeight="1" s="31">
-      <c r="B16" s="49" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="73" t="inlineStr">
+        <is>
+          <t>Travel Subtotal</t>
+        </is>
+      </c>
+      <c r="C16" s="74">
+        <f>SUM(C12:C15)</f>
+        <v/>
+      </c>
+      <c r="D16" s="74">
+        <f>SUM(D12:D15)</f>
+        <v/>
+      </c>
+      <c r="E16" s="74">
+        <f>SUM(E12:E15)</f>
+        <v/>
+      </c>
+      <c r="F16" s="74">
+        <f>SUM(F12:F15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="67" t="inlineStr">
         <is>
           <t>SUBCONTRACTS</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="30" customHeight="1" s="31">
-      <c r="B17" s="50" t="inlineStr">
+      <c r="C18" s="68" t="n"/>
+      <c r="D18" s="68" t="n"/>
+      <c r="E18" s="68" t="n"/>
+      <c r="F18" s="68" t="n"/>
+      <c r="G18" s="68" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="69" t="inlineStr">
         <is>
           <t>Cybersecurity Toolset Provider</t>
         </is>
       </c>
-      <c r="C17" s="40" t="n">
+      <c r="C19" s="70" t="n">
         <v>250000</v>
       </c>
-      <c r="D17" s="40" t="n">
+      <c r="D19" s="70" t="n">
         <v>250000</v>
       </c>
-      <c r="E17" s="40" t="n">
+      <c r="E19" s="70" t="n">
         <v>250000</v>
       </c>
-      <c r="F17" s="41">
-        <f>C17+D17+E17</f>
-        <v/>
-      </c>
-      <c r="G17" s="51" t="inlineStr">
+      <c r="F19" s="71">
+        <f>C19+D19+E19</f>
+        <v/>
+      </c>
+      <c r="G19" s="72" t="inlineStr">
         <is>
           <t>CMMC compliance tools and monitoring; FFP subcontract</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1" s="31">
-      <c r="B18" s="50" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="69" t="inlineStr">
         <is>
           <t>Specialized Testing Lab</t>
         </is>
       </c>
-      <c r="C18" s="40" t="n">
+      <c r="C20" s="70" t="n">
         <v>75000</v>
       </c>
-      <c r="D18" s="40" t="n">
+      <c r="D20" s="70" t="n">
         <v>75000</v>
       </c>
-      <c r="E18" s="40" t="n">
+      <c r="E20" s="70" t="n">
         <v>50000</v>
       </c>
-      <c r="F18" s="41">
-        <f>C18+D18+E18</f>
-        <v/>
-      </c>
-      <c r="G18" s="51" t="inlineStr">
+      <c r="F20" s="71">
+        <f>C20+D20+E20</f>
+        <v/>
+      </c>
+      <c r="G20" s="72" t="inlineStr">
         <is>
           <t>IV&amp;V testing; reduced Y3 as system matures</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20" ht="21.75" customHeight="1" s="31">
-      <c r="B20" s="49" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="73" t="inlineStr">
+        <is>
+          <t>Subcontracts Subtotal</t>
+        </is>
+      </c>
+      <c r="C21" s="74">
+        <f>SUM(C19:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="74">
+        <f>SUM(D19:D20)</f>
+        <v/>
+      </c>
+      <c r="E21" s="74">
+        <f>SUM(E19:E20)</f>
+        <v/>
+      </c>
+      <c r="F21" s="74">
+        <f>SUM(F19:F20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="67" t="inlineStr">
         <is>
           <t>OTHER</t>
         </is>
       </c>
-    </row>
-    <row r="21" ht="30" customHeight="1" s="31">
-      <c r="B21" s="50" t="inlineStr">
+      <c r="C23" s="68" t="n"/>
+      <c r="D23" s="68" t="n"/>
+      <c r="E23" s="68" t="n"/>
+      <c r="F23" s="68" t="n"/>
+      <c r="G23" s="68" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="69" t="inlineStr">
         <is>
           <t>Training &amp; Certification</t>
         </is>
       </c>
-      <c r="C21" s="40" t="n">
+      <c r="C24" s="70" t="n">
         <v>20000</v>
       </c>
-      <c r="D21" s="40" t="n">
+      <c r="D24" s="70" t="n">
         <v>15000</v>
       </c>
-      <c r="E21" s="40" t="n">
+      <c r="E24" s="70" t="n">
         <v>15000</v>
       </c>
-      <c r="F21" s="41">
-        <f>C21+D21+E21</f>
-        <v/>
-      </c>
-      <c r="G21" s="51" t="inlineStr">
+      <c r="F24" s="71">
+        <f>C24+D24+E24</f>
+        <v/>
+      </c>
+      <c r="G24" s="72" t="inlineStr">
         <is>
           <t>PMP, ITIL, Security+ certifications; initial ramp Y1</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1" s="31">
-      <c r="B22" s="50" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="69" t="inlineStr">
         <is>
           <t>Communications (SIPR/NIPR)</t>
         </is>
       </c>
-      <c r="C22" s="40" t="n">
+      <c r="C25" s="70" t="n">
         <v>18000</v>
       </c>
-      <c r="D22" s="40" t="n">
+      <c r="D25" s="70" t="n">
         <v>18000</v>
       </c>
-      <c r="E22" s="40" t="n">
+      <c r="E25" s="70" t="n">
         <v>18000</v>
       </c>
-      <c r="F22" s="41">
-        <f>C22+D22+E22</f>
-        <v/>
-      </c>
-      <c r="G22" s="51" t="inlineStr">
+      <c r="F25" s="71">
+        <f>C25+D25+E25</f>
+        <v/>
+      </c>
+      <c r="G25" s="72" t="inlineStr">
         <is>
           <t>Secure communication lines and VPN services</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24" ht="15" customHeight="1" s="31">
-      <c r="B24" s="52" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="73" t="inlineStr">
+        <is>
+          <t>Other Subtotal</t>
+        </is>
+      </c>
+      <c r="C26" s="74">
+        <f>SUM(C24:C25)</f>
+        <v/>
+      </c>
+      <c r="D26" s="74">
+        <f>SUM(D24:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="74">
+        <f>SUM(E24:E25)</f>
+        <v/>
+      </c>
+      <c r="F26" s="74">
+        <f>SUM(F24:F25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="75" t="inlineStr">
         <is>
           <t>TOTAL ODC &amp; TRAVEL</t>
         </is>
       </c>
-      <c r="C24" s="53">
-        <f>SUM(C5:C22)</f>
-        <v/>
-      </c>
-      <c r="D24" s="53">
-        <f>SUM(D5:D22)</f>
-        <v/>
-      </c>
-      <c r="E24" s="53">
-        <f>SUM(E5:E22)</f>
-        <v/>
-      </c>
-      <c r="F24" s="53">
-        <f>SUM(F5:F22)</f>
-        <v/>
-      </c>
-      <c r="G24" s="43" t="n"/>
-    </row>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27" ht="15" customHeight="1" s="31">
-      <c r="B27" s="47" t="inlineStr">
+      <c r="C28" s="76">
+        <f>C9+C16+C21+C26</f>
+        <v/>
+      </c>
+      <c r="D28" s="76">
+        <f>D9+D16+D21+D26</f>
+        <v/>
+      </c>
+      <c r="E28" s="76">
+        <f>E9+E16+E21+E26</f>
+        <v/>
+      </c>
+      <c r="F28" s="76">
+        <f>F9+F16+F21+F26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="77" t="inlineStr">
         <is>
           <t>Template by Acqlerate — Defense Acquisitions Academy | www.acqlerate.com</t>
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="B32" s="77" t="inlineStr">
+        <is>
+          <t>Generated: September 2026 | Updated: FAC 2025-06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B27:G27"/>
-  </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="B2:F47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" style="30" min="1" max="1"/>
-    <col width="30" customWidth="1" style="30" min="2" max="2"/>
-    <col width="16" customWidth="1" style="30" min="3" max="5"/>
-    <col width="18" customWidth="1" style="30" min="6" max="6"/>
+    <col width="2.5" customWidth="1" style="31" min="1" max="1"/>
+    <col width="30" customWidth="1" style="31" min="2" max="2"/>
+    <col width="14" customWidth="1" style="31" min="3" max="3"/>
+    <col width="14" customWidth="1" style="31" min="4" max="4"/>
+    <col width="14" customWidth="1" style="31" min="5" max="5"/>
+    <col width="14" customWidth="1" style="31" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="30" customHeight="1" s="31">
-      <c r="B2" s="32" t="inlineStr">
+    <row r="2">
+      <c r="B2" s="78" t="inlineStr">
         <is>
           <t>IGCE Summary — Total Program Estimate</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="31">
-      <c r="B3" s="33" t="inlineStr">
-        <is>
-          <t>Rolls up Labor and ODC estimates for total independent government cost estimate</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
-    <row r="5" ht="15" customHeight="1" s="31">
-      <c r="B5" s="48" t="inlineStr">
+    <row r="3">
+      <c r="B3" s="79" t="inlineStr">
+        <is>
+          <t>Rolls up Labor and ODC estimates by cost category for the total independent government cost estimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="66" t="inlineStr">
         <is>
           <t>Cost Element</t>
         </is>
       </c>
-      <c r="C5" s="48" t="inlineStr">
+      <c r="C5" s="66" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
-      <c r="D5" s="48" t="inlineStr">
+      <c r="D5" s="66" t="inlineStr">
         <is>
           <t>Year 2</t>
         </is>
       </c>
-      <c r="E5" s="48" t="inlineStr">
+      <c r="E5" s="66" t="inlineStr">
         <is>
           <t>Year 3</t>
         </is>
       </c>
-      <c r="F5" s="48" t="inlineStr">
+      <c r="F5" s="66" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="31">
-      <c r="B6" s="54" t="inlineStr">
-        <is>
-          <t>Total Labor (Loaded)</t>
-        </is>
-      </c>
-      <c r="C6" s="55">
+    <row r="6">
+      <c r="B6" s="69" t="inlineStr">
+        <is>
+          <t>Labor (Loaded)</t>
+        </is>
+      </c>
+      <c r="C6" s="71">
         <f>'Labor Estimate'!K17</f>
         <v/>
       </c>
-      <c r="D6" s="55">
+      <c r="D6" s="71">
         <f>'Labor Estimate'!L17</f>
         <v/>
       </c>
-      <c r="E6" s="55">
+      <c r="E6" s="71">
         <f>'Labor Estimate'!M17</f>
         <v/>
       </c>
-      <c r="F6" s="55">
+      <c r="F6" s="71">
         <f>'Labor Estimate'!N17</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="31">
-      <c r="B7" s="54" t="inlineStr">
-        <is>
-          <t>Total ODC &amp; Travel</t>
-        </is>
-      </c>
-      <c r="C7" s="55">
-        <f>'ODC &amp; Travel'!C24</f>
-        <v/>
-      </c>
-      <c r="D7" s="55">
-        <f>'ODC &amp; Travel'!D24</f>
-        <v/>
-      </c>
-      <c r="E7" s="55">
-        <f>'ODC &amp; Travel'!E24</f>
-        <v/>
-      </c>
-      <c r="F7" s="55">
-        <f>'ODC &amp; Travel'!F24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9" ht="15" customHeight="1" s="31">
-      <c r="B9" s="56" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="69" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="C7" s="71">
+        <f>'ODC &amp; Travel'!C9</f>
+        <v/>
+      </c>
+      <c r="D7" s="71">
+        <f>'ODC &amp; Travel'!D9</f>
+        <v/>
+      </c>
+      <c r="E7" s="71">
+        <f>'ODC &amp; Travel'!E9</f>
+        <v/>
+      </c>
+      <c r="F7" s="71">
+        <f>'ODC &amp; Travel'!F9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="69" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="C8" s="71">
+        <f>'ODC &amp; Travel'!C16</f>
+        <v/>
+      </c>
+      <c r="D8" s="71">
+        <f>'ODC &amp; Travel'!D16</f>
+        <v/>
+      </c>
+      <c r="E8" s="71">
+        <f>'ODC &amp; Travel'!E16</f>
+        <v/>
+      </c>
+      <c r="F8" s="71">
+        <f>'ODC &amp; Travel'!F16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="69" t="inlineStr">
+        <is>
+          <t>Subcontracts</t>
+        </is>
+      </c>
+      <c r="C9" s="71">
+        <f>'ODC &amp; Travel'!C21</f>
+        <v/>
+      </c>
+      <c r="D9" s="71">
+        <f>'ODC &amp; Travel'!D21</f>
+        <v/>
+      </c>
+      <c r="E9" s="71">
+        <f>'ODC &amp; Travel'!E21</f>
+        <v/>
+      </c>
+      <c r="F9" s="71">
+        <f>'ODC &amp; Travel'!F21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="69" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C10" s="71">
+        <f>'ODC &amp; Travel'!C26</f>
+        <v/>
+      </c>
+      <c r="D10" s="71">
+        <f>'ODC &amp; Travel'!D26</f>
+        <v/>
+      </c>
+      <c r="E10" s="71">
+        <f>'ODC &amp; Travel'!E26</f>
+        <v/>
+      </c>
+      <c r="F10" s="71">
+        <f>'ODC &amp; Travel'!F26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="75" t="inlineStr">
         <is>
           <t>GRAND TOTAL (IGCE)</t>
         </is>
       </c>
-      <c r="C9" s="57">
-        <f>SUM(C6:C7)</f>
-        <v/>
-      </c>
-      <c r="D9" s="57">
-        <f>SUM(D6:D7)</f>
-        <v/>
-      </c>
-      <c r="E9" s="57">
-        <f>SUM(E6:E7)</f>
-        <v/>
-      </c>
-      <c r="F9" s="57">
-        <f>SUM(F6:F7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12" ht="16.15" customHeight="1" s="31">
-      <c r="B12" s="58" t="inlineStr">
+      <c r="C12" s="76">
+        <f>SUM(C6:C10)</f>
+        <v/>
+      </c>
+      <c r="D12" s="76">
+        <f>SUM(D6:D10)</f>
+        <v/>
+      </c>
+      <c r="E12" s="76">
+        <f>SUM(E6:E10)</f>
+        <v/>
+      </c>
+      <c r="F12" s="76">
+        <f>SUM(F6:F10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="80" t="inlineStr">
         <is>
           <t>IGCE Requirements &amp; Notes</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1" s="31">
-      <c r="B13" s="59" t="inlineStr">
+    <row r="33">
+      <c r="B33" s="81" t="inlineStr">
         <is>
           <t>1. This IGCE was prepared in accordance with FAR 36.203 and agency IGCE guidelines. It represents the government's best estimate of anticipated contract costs.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1" s="31">
-      <c r="B14" s="59" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="81" t="inlineStr">
         <is>
           <t>2. Labor rates are based on market research of comparable DoD contracts, GSA Schedule rates, and Bureau of Labor Statistics (BLS) occupational data.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1" s="31">
-      <c r="B15" s="59" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="81" t="inlineStr">
         <is>
           <t>3. Indirect rates (fringe, overhead, G&amp;A) are estimated based on DCAA audit data for similarly sized defense contractors in the applicable geographic region.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1" s="31">
-      <c r="B16" s="59" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="81" t="inlineStr">
         <is>
           <t>4. Travel estimates are based on Joint Travel Regulations (JTR) per diem rates and General Services Administration (GSA) city pair airfares.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1" s="31">
-      <c r="B17" s="59" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="81" t="inlineStr">
         <is>
           <t>5. Fee/profit is NOT included. For cost-reimbursement contracts, fee will be negotiated per FAR 15.404-4 (weighted guidelines method).</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1" s="31">
-      <c r="B18" s="59" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="81" t="inlineStr">
         <is>
           <t>6. A ±10% accuracy range is expected for this estimate. Final negotiated costs may vary based on contractor proposals and competitive dynamics.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1" s="31">
-      <c r="B19" s="59" t="inlineStr">
+    <row r="39">
+      <c r="B39" s="81" t="inlineStr">
         <is>
           <t>7. This IGCE should be updated whenever significant changes occur to the PWS/SOW, period of performance, or economic conditions.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1" s="31">
-      <c r="B20" s="59" t="inlineStr">
+    <row r="40">
+      <c r="B40" s="81" t="inlineStr">
         <is>
           <t>8. The IGCE is procurement-sensitive and should be marked FOUO / Source Selection Sensitive until after contract award.</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23" ht="15" customHeight="1" s="31">
-      <c r="B23" s="47" t="inlineStr">
+    <row r="43">
+      <c r="B43" s="77" t="inlineStr">
         <is>
           <t>Template by Acqlerate — Defense Acquisitions Academy | www.acqlerate.com</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="31">
-      <c r="B24" s="47" t="inlineStr">
-        <is>
-          <t>Generated: April 2026 | Updated: FAC 2025-07</t>
+    <row r="44">
+      <c r="B44" s="77" t="inlineStr">
+        <is>
+          <t>Generated: September 2026 | Updated: FAC 2025-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="82" t="inlineStr">
+        <is>
+          <t>License &amp; Use</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="83" t="inlineStr">
+        <is>
+          <t>This template is licensed for use on one program, by one organization, under your Acqlerate purchase. Customize the text, branding, and layout freely for your own program. Deploying it company-wide, sharing it outside your organization, or reselling it requires an Acqlerate Team License (acqlerate.com/team).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B13:F13"/>
-  </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>